--- a/Final_Summary_Result_Pro.xlsx
+++ b/Final_Summary_Result_Pro.xlsx
@@ -474,24 +474,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="33" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,50 +523,55 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>MCU</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Feature Support_Wi-Fi</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Feature Support_BT</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Feature Support_Z-Wave</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Feature Support_NFC</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Feature Support_Zigbee</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Feature Support_Thread</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Feature Support_Matter</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Dimension(L W H)</t>
-        </is>
-      </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
           <t>Maximum(ideal) Throughput(Mbps)</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Link to Datasheet</t>
         </is>
@@ -599,19 +605,19 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
           <t>Wi-Fi 6 ax mode</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>BT 5.3</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
           <t>NA</t>
@@ -634,15 +640,20 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
           <t>15 x 13 x 1.55 MM</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="O2" s="5">
+      <c r="P2" s="5">
         <f>HYPERLINK("https://drive.google.com/file/d/1LfK1qYihneOijAYs7II_bUxGP-xfjoJ4/view?usp=drivesdk", "Link")</f>
         <v/>
       </c>
@@ -675,19 +686,19 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>Wi-Fi 6E ax mode</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>BT 5.3</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
           <t>NA</t>
@@ -700,25 +711,30 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
           <t>Thread</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
           <t>12 x 12 x 1.95 MM</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="O3" s="5">
+      <c r="P3" s="5">
         <f>HYPERLINK("https://drive.google.com/file/d/1HaKu0qd7E2G0mm9lTRFfWTZv-Ov1_U1C/view?usp=drivesdk", "Link")</f>
         <v/>
       </c>
@@ -751,19 +767,19 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Wi-Fi 5 ac mode</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>BT 5.4</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>NA</t>
@@ -786,15 +802,20 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
           <t>15 x 13 x 1.85 MM</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>867</t>
         </is>
       </c>
-      <c r="O4" s="5">
+      <c r="P4" s="5">
         <f>HYPERLINK("https://drive.google.com/file/d/1Z26XQMUd3kE1mo8FiDdIyeZKyh0xXRxU/view?usp=drivesdk", "Link")</f>
         <v/>
       </c>
@@ -827,19 +848,19 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>Wi-Fi 6E ax mode</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>BT 6.0</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>NA</t>
@@ -847,40 +868,127 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
           <t>Zigbee</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Thread</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>12 x 12 x 1.82 MM</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="O5" s="5">
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>114.7</t>
+        </is>
+      </c>
+      <c r="P5" s="5">
         <f>HYPERLINK("https://drive.google.com/file/d/1oNlzAuPo1ZV6paLLs70eMZfQGG7gaNc1/view?usp=drivesdk", "Link")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Cortex-M33 &amp; WI-FI 6 &amp; BT 5.3 &amp; Matter Module</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>AzureWave</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>AW-CU642</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ax 20MHz</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Cortex-M33</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6 ax mode</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>BT 5.3</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Matter</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>16 x 25 MM</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P6" s="5">
+        <f>HYPERLINK("https://drive.google.com/file/d/11XROdg0yF_HsD5Pa8jCH_lEINRjTpZgW/view?usp=drivesdk", "Link")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Final_Summary_Result_Pro.xlsx
+++ b/Final_Summary_Result_Pro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_data_Foxconn\F_data\others\RF Integrated Conversion Tool\pdf_tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_data_Foxconn\F_data\others\RF Integrated Conversion Tool\pdf_tool\Summary_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D7B0A3-4EAB-43A8-B24C-DDBC770FC690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3F2C34-F661-4903-8297-E09CBF626CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="135">
   <si>
     <t>Description</t>
   </si>
@@ -481,6 +481,26 @@
   </si>
   <si>
     <t>Z-wave &amp; BT 5.3 with MCU</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Link</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6233A-SRB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fn-Link</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BT 5.2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12x12 MM</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -902,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
@@ -1993,6 +2013,56 @@
         <v>Link</v>
       </c>
     </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="O22" s="2">
+        <v>150</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -2016,6 +2086,7 @@
     <hyperlink ref="P19" r:id="rId18" display="https://drive.google.com/file/d/1jT05zm-07VXdXQVMkX_fkHUpF08Bocq2/view?usp=drivesdk" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="P20" r:id="rId19" display="https://drive.google.com/file/d/1ndiN_0xDTRnKKdv32id-AACsf5JMvIgd/view?usp=drivesdk" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
     <hyperlink ref="P21" r:id="rId20" display="https://drive.google.com/file/d/1GFuWb3xBw_b0_qPAEcJe4U71XjEMjqPG/view?usp=drivesdk" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="P22" r:id="rId21" display="https://drive.google.com/file/d/1i0AeqZoohpgV9pcNxVhHh1HRQRkCURfB/view?usp=drivesdk" xr:uid="{D7784191-865E-4692-99A3-817169725E7C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Final_Summary_Result_Pro.xlsx
+++ b/Final_Summary_Result_Pro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_data_Foxconn\F_data\others\RF Integrated Conversion Tool\pdf_tool\Summary_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3F2C34-F661-4903-8297-E09CBF626CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47A52FB-0A10-4395-958B-4116F61C6007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="134">
   <si>
     <t>Description</t>
   </si>
@@ -481,10 +481,6 @@
   </si>
   <si>
     <t>Z-wave &amp; BT 5.3 with MCU</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Link</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2018,10 +2014,10 @@
         <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>25</v>
@@ -2036,31 +2032,32 @@
         <v>81</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="O22" s="2">
         <v>150</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>130</v>
+      <c r="P22" s="3" t="str">
+        <f>HYPERLINK("https://drive.google.com/file/d/1i0AeqZoohpgV9pcNxVhHh1HRQRkCURfB/view?usp=drivesdk", "Link")</f>
+        <v>Link</v>
       </c>
     </row>
   </sheetData>

--- a/Final_Summary_Result_Pro.xlsx
+++ b/Final_Summary_Result_Pro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_data_Foxconn\F_data\others\RF Integrated Conversion Tool\pdf_tool\Summary_backup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_data_Foxconn\F_data\others\RF Integrated Conversion Tool\pdf_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47A52FB-0A10-4395-958B-4116F61C6007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD82855-2751-437C-840C-77841CF2DB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="136">
   <si>
     <t>Description</t>
   </si>
@@ -484,19 +484,26 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>6233A-SRB</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fn-Link</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>BT 5.2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12x12 MM</t>
+    <t>TRIDENT</t>
+  </si>
+  <si>
+    <t>1X1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>T32CZ20</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARM Cortex®-M33</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>QFN40 5x5mm</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z-wave with MCU</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -600,7 +607,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -614,6 +621,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1918,7 +1929,7 @@
         <v>123</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>19</v>
@@ -1969,7 +1980,7 @@
         <v>127</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>19</v>
@@ -2011,31 +2022,31 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>19</v>
@@ -2050,13 +2061,13 @@
         <v>19</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="O22" s="2">
-        <v>150</v>
-      </c>
-      <c r="P22" s="3" t="str">
-        <f>HYPERLINK("https://drive.google.com/file/d/1i0AeqZoohpgV9pcNxVhHh1HRQRkCURfB/view?usp=drivesdk", "Link")</f>
+        <v>134</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P22" s="6" t="str">
+        <f>HYPERLINK("https://drive.google.com/file/d/1_sVvE2-bexORprmbD1rp-NOKxjrBYqb-/view?usp=drivesdk", "Link")</f>
         <v>Link</v>
       </c>
     </row>
@@ -2083,7 +2094,7 @@
     <hyperlink ref="P19" r:id="rId18" display="https://drive.google.com/file/d/1jT05zm-07VXdXQVMkX_fkHUpF08Bocq2/view?usp=drivesdk" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="P20" r:id="rId19" display="https://drive.google.com/file/d/1ndiN_0xDTRnKKdv32id-AACsf5JMvIgd/view?usp=drivesdk" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
     <hyperlink ref="P21" r:id="rId20" display="https://drive.google.com/file/d/1GFuWb3xBw_b0_qPAEcJe4U71XjEMjqPG/view?usp=drivesdk" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="P22" r:id="rId21" display="https://drive.google.com/file/d/1i0AeqZoohpgV9pcNxVhHh1HRQRkCURfB/view?usp=drivesdk" xr:uid="{D7784191-865E-4692-99A3-817169725E7C}"/>
+    <hyperlink ref="P22" r:id="rId21" display="https://drive.google.com/file/d/1GFuWb3xBw_b0_qPAEcJe4U71XjEMjqPG/view?usp=drivesdk" xr:uid="{00C7B131-FC4E-4B68-8C63-7FC3DAB87632}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
